--- a/vragen/geschrapte_vragen.xlsx
+++ b/vragen/geschrapte_vragen.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="Geschrapt" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Geschrapt'!$A$1:$S$41</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,28 +28,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -72,19 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,2337 +425,2636 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="74" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>In gebruik</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Categorie (was)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Vraag NL</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Vraag EN (zoekhulp)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Antwoord</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bron (bestaand)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Bron (jouw aanvulling)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Commons-fotolink</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Verwijderen</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Advies Claude</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jouw opmerking</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Let op</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Bron (geverifieerd)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Bewijszin</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Controle</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Vertrouwen bron</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Status oude bron</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" t="n">
         <v>68</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hoe lang waren de langste mouwen aan een kledingstuk ooit in meters?</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>How long were the longest sleeves on a garment ever in metres?</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" t="n">
         <v>51</v>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" t="n">
         <v>188</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hoeveel minuten kook je een ei voor een zacht gekookt ei?</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>How many minutes do you cook an egg for a soft boiled egg?</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" t="n">
         <v>189</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hoeveel rundvleesburgers verkocht McDonald’s wereldwijd in 2023?</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>How many beef burgers sold McDonalds worldwide in 2023?</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>44000000000</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://corporate.mcdonalds.com/corpmcd/our-company/annual-reports.html</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>McDonald's telt sinds 1994 geen verkochte hamburgers meer en publiceert dit getal niet. Schattingen liggen tussen 2,4 en 6,5 miljard per jaar; 44 miljard is een orde van grootte te hoog.</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>geen bron mogelijk (fout)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" t="n">
         <v>284</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Geografie</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Geografie</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Hoeveel landen liggen volledig op het zuidelijk halfrond?</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>How many countries are in the southern hemisphere?</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>32</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>World Atlas is not definitive; classification depends on boundary convention.</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Het antwoord hangt af van de gekozen grensconventie; de oorspronkelijke bron zei dat zelf al. Geen vaste telling mogelijk.</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" t="n">
         <v>381</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hoeveel centimeter lang is een standaard das bij het strikken?</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>How many centimeters is a standard tie when you tie?</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>145</v>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" t="n">
         <v>382</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hoeveel gaten heeft een standaard schoenveter meestal in één schoen?</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>How many holes does a standard shoelace usually have in one shoe?</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" t="n">
         <v>384</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Mode en lifestyle</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hoeveel millimeter breed is een standaard herenhorlogeband?</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>How many millimeters wide is a standard men's watch band?</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>22</v>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" t="n">
         <v>446</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hoe lang was de langste snoepstaaf ooit in kilometer?</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>How long was the longest candy bar ever in kilometres?</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" t="n">
         <v>451</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hoeveel kilometer was de langste zwemtocht ooit?</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>How many kilometres was the longest swim ever?</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>500</v>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" t="n">
         <v>457</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>puzzel</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Records en vergelijkingen</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hoeveel voertuigen stonden er ongeveer in de langste file ooit?</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>How many vehicles were in the longest traffic traffic ever?</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" t="n">
         <v>633</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Landbouw en industrie</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Dieren</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hoeveel bijenkorven produceert de gemiddelde Ethiopische bijenhouder per jaar?</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" t="n">
         <v>638</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Dieren</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Dieren</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hoeveel eieren legt een kangoeroe per worp?</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="n">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" t="n">
         <v>688</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Dieren</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Dieren</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hoeveel van de 10 giftigste slangen ter wereld komen voor in Australië?</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="n">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" t="n">
         <v>708</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hoeveel gram weegt een standaard chocoladereep vaak?</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>How many grams does a standard chocolate bar often weigh?</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>No universal standard; depends on product and market.</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Chocoladerepen hebben geen standaardgewicht; het verschilt per merk en land.</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" t="n">
         <v>769</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Filosofie, psychologie en religie</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Filosofie, psychologie en religie</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hoeveel zwaarden waren er volgens de legende van koning Arthur beschikbaar?</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>How many swords were available according to King Arthur's legend?</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" t="n">
         <v>806</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Gebouwen en infrastructuur</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Gebouwen en infrastructuur</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hoeveel piramides staan er ongeveer in Gizeh?</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>How many pyramids are there in Giza?</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>https://www.britannica.com/place/Pyramids-of-Giza</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Giza_pyramid_complex</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Dubbel met vraag 241, en "ongeveer" past niet bij een exact getal. Gizeh telt drie hoofdpiramides maar met de koninginnenpiramides erbij negen.</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>onbruikbaar</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>vraag deugt niet, zie toelichting</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" t="n">
         <v>808</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Gebouwen en infrastructuur</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Gebouwen en infrastructuur</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hoeveel rivieren bruggen telt Sydney Harbour?</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="n">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Onleesbaar: "rivieren bruggen telt Sydney Harbour".</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" t="n">
         <v>837</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Geografie</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Geografie</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hoeveel Europese landen liggen er niet op het vasteland (exclusief eilanden) in de EU als eilandstaten?</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>How many European countries are not on the mainland (excluding islands) in the EU as island states?</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Onleesbaar geformuleerd ("liggen er niet op het vasteland (exclusief eilanden) als eilandstaten").</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>De vraag spreekt zichzelf tegen: "niet op het vasteland (exclusief eilanden)". Bovendien zijn Ierland, Malta en Cyprus alle drie eilandstaten in de EU, dus het antwoord twee klopt hoe dan ook niet.</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>vraag deugt niet (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" t="n">
         <v>1116</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hoeveel snaarinstrumenten bevat de klassieke Japanse koto-ensemble van hoort?</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>How many string instruments does the classic Japanese koto ensemble contain?</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" t="n">
         <v>13</v>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Onafgemaakte zin: "koto-ensemble van hoort".</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" t="n">
         <v>1119</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hoeveel snaren heeft de West-Afrikaanse djembé als trommel?</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="n">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Feitelijk onjuist: een djembé is een trommel en heeft geen snaren.</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" t="n">
         <v>1124</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hoeveel snaren heeft de klassieke Mexicaanse mariachi-gitarron (bajo sexto)?</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>How many strings does the classic Mexican mariachi-gitarron (bajo sexto) have?</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" t="n">
         <v>12</v>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Verwart twee instrumenten: een guitarrón is geen bajo sexto.</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" t="n">
         <v>1146</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Dagelijks leven</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hoeveel NL-postcodes cijfers heeft een Nederlandse postcode standaard (vier cijfers plus twee letters)?</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>How many NL postal code numbers has a Dutch postal code standard (four digits plus two letters)?</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Het antwoord staat letterlijk in de vraag ("vier cijfers plus twee letters").</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" t="n">
         <v>1155</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Muziek</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hoeveel bruggen telt het klassieke orkestnummer Bruggetje van Sainte Anneï in de titel niet?</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>"Bruggetje van Sainte Anneï" bestaat niet; de vraag ontkent zichzelf.</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" t="n">
         <v>1156</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hoeveel dagen duurt de Alvleeskliervlaamse Wielerweek Vredeskoers niet?</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>How many days does the All-Flemish Wheeler Week Peace course not last?</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>"Alvleeskliervlaamse Wielerweek" is verzonnen (alvleesklier = orgaan).</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" t="n">
         <v>1157</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Kunst en cultuur</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Hoeveel dagen duurt de Nederlands Dans Theater-productie Stop-Motion doorgaans per seizoensblok?</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>How many days does the Dutch Dance Theater production Stop-Motion usually last per seasonal block?</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Verzonnen meeteenheid: "per seizoensblok".</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" t="n">
         <v>1163</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Economie &amp; geld</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hoeveel eenheden telt de Nederlandse duizendguldenbiljet-collectie uit 1970?</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>How many units does the 1970 Dutch thousand guilder banknote collection have?</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Verzonnen: er bestaat geen "duizendguldenbiljet-collectie uit 1970".</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>"De duizendguldenbiljet-collectie uit 1970" bestaat niet als begrip, en het antwoord een maakt elke deelsom stuk.</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>vraag deugt niet (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" t="n">
         <v>1170</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hoeveel gram boter gaat in de klassieke Nederlandse boterkoek per 10 porties?</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>How many grams of butter goes into the classic Dutch buttercake per 10 portions?</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" t="n">
         <v>250</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" t="n">
         <v>1171</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hoeveel gram suiker bevat een standaard reep chocolade van Droste van 100 gram ongeveer?</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>55</v>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" t="n">
         <v>1172</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Eten &amp; drinken</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hoeveel gram weegt een stroopwafel van het merk Daelmans standaard?</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>How many grams does a syrup waffle of the Daelmans standard weigh?</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" t="n">
         <v>32</v>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr"/>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" t="n">
         <v>1175</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Spellen en speelgoed</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hoeveel kapstokkaarten telt een standaard Nederlandse Mens-erger-je-niet?</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>How many card cards does a standard Dutch Mens-erger-je-not have?</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>"Kapstokkaarten" bestaan niet in Mens-erger-je-niet.</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" t="n">
         <v>1177</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Dagelijks leven</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hoeveel keer per jaar publiceert het CBS de driejaarlijkse woondenquête?</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>How many times a year does the CBS publish the three-yearly living survey?</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Spreekt zichzelf tegen: "per jaar" versus "driejaarlijkse".</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="4" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" t="n">
         <v>1198</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Politiek en recht</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hoeveel koppen bevat de Nederlandse driehoek bestuursniveaus (rijk, provincie, gemeente)?</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>How many headlines does the Dutch triangle contain levels of government (rich, province, municipality)?</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>"Koppen" is hier onzin; het antwoord staat in de vraag.</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr"/>
-      <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" t="n">
         <v>1203</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Geschiedenis</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Nederlands</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hoeveel landen kocht de VOC formeel aan als koloniale gebieden?</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>De VOC kocht geen landen; feitelijk onjuiste premisse.</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="4" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" t="n">
         <v>1258</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Politiek en recht</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Politiek en recht</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hoeveel emiraten heeft Saoedi-Arabië als koninkrijk in bestuurlijke regio (provincies)?</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>How many emirates has Saudi Arabia as a kingdom in administrative region (provincies)?</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" t="n">
         <v>13</v>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Feitelijk onjuist: Saoedi-Arabië heeft geen emiraten.</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr"/>
-      <c r="P35" s="4" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" t="n">
         <v>1287</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Politiek en recht</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Politiek en recht</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Hoeveel rechterzittingen telt het Amerikaanse Hooggerechtshof?</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>How many court hearings does the U.S. Supreme Court have?</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" t="n">
         <v>9</v>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Vraagt naar "rechterzittingen"; bedoeld is het aantal rechters.</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr"/>
-      <c r="P36" s="4" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" t="n">
         <v>1374</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Hoeveel kuiven heeft een honkbalveld (bases plus home plate)?</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>How many coves has a baseball field (bases plus home plates)?</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>"Kuiven" bestaat niet in deze betekenis; bedoeld zijn honkholtes of bases.</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr"/>
-      <c r="P37" s="4" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" t="n">
         <v>1394</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hoeveel proloog kilometers telt een Tour de France etappe bijna nooit?</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Dubbele ontkenning ("telt een etappe bijna nooit") maakt het onbeantwoordbaar.</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr"/>
-      <c r="P38" s="4" t="inlineStr"/>
-      <c r="Q38" s="3" t="inlineStr"/>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
         <is>
           <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" t="n">
         <v>1400</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Sport</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Hoeveel rings heeft het NBA-logo in het midden?</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>How many rings does the NBA logo have in the middle?</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>"Rings" is Engels blijven staan; het NBA-logo heeft geen ringen.</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>geen bron</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr"/>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Het NBA-logo is een silhouet van een basketballer en heeft geen ringen. De vraag klopt niet, en het antwoord een maakt elke deelsom stuk.</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
         <is>
           <t>vraag deugt niet (onbruikbaar)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" t="n">
         <v>1457</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Technologie</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Technologie</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hoeveel megabytes zitten er in precies één gigabyte?</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="n">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>1024</v>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>https://physics.nist.gov/cuu/Units/binary.html</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>Vraagt hoeveel megabyte in "precies een gigabyte" gaan; dat zijn er 1000, niet 1024. Vraag 1458 stelt dezelfde vraag mét de binaire voorwaarde en is daarmee correct. Deze vraag is een dubbele met een fout antwoord.</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://physics.nist.gov/cuu/Units/binary.html</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>De vraag zegt "precies een gigabyte", en dan is het antwoord 1000 megabyte. De 1024 hoort bij de gibibyte. Vraag 1458 stelt dezelfde vraag wel goed.</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>onbruikbaar</t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>vraag vervallen</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" t="n">
         <v>1472</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Technologie</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Technologie</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>In welk jaar werd de Toyota motorfiets eerste gebouwd - nee Toyota is auto (1885 Daimler - dit zit niet in Azië)?</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Bevat de redactienotitie "nee Toyota is auto (1885 Daimler - dit zit niet in Azië)".</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="4" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>geen bron mogelijk (onbruikbaar)</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Kunst en cultuur</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kunst en cultuur</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Hoeveel natuursonden (beelden) staan er op Paaseiland - sorry dat zit niet in Europa!</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>How many scenes of nature are there on Easter Island - sorry that's not in Europe!</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bevat de redactienotitie "sorry dat zit niet in Europa!"; "natuursonden" is bovendien geen woord.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Paaseiland</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bahn (2002), The enigma's of Easter Island, Oxford University Press, ISBN 0-19-280340-9
+Externe link
+(en)  Korte documentaire van David Attenborough over Paaseiland
+Referenties</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Geografie</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nederlands</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Hoeveel eilanden telt de Nederlandse Antillen in de huidige status van landen?</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>geen bron · geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlandse_Antillen</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>De leeftijdsopbouw was:
+0-14 jaar 23,9%
+15-65 jaar 67,3%
+66 jaar en ouder 8,7%
+De levensverwachting was:
+Totale bevolking 76,03 jaar
+Mannen 73,76 jaar
+Vrouwen 78,41 jaar
+De Nederlandse Antillen had een bevolkingsgroei van 0,79%.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nederlands</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Hoeveel landen deden er mee aan het Nederlands kampioenschap wielrennen voor clubs?</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>How many countries participated in the Dutch cycling championship for clubs?</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Een nationaal kampioenschap heeft per definitie één land.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlands</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Het Nederlands alleen wordt door meer mensen gesproken dan de Noord-Germaanse (Scandinavische) talen bij elkaar: Zweeds (10 miljoen), Noors (5 miljoen), Deens (5 miljoen) en IJslands (0,3 miljoen).</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Politiek en recht</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Nederlands</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Hoeveel landen stemden vóór het Nederlands als EU-taal?</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Verzonnen stemming; zo werkt de EU-talenregeling niet.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>geen bron · geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlands</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Het Nederlands alleen wordt door meer mensen gesproken dan de Noord-Germaanse (Scandinavische) talen bij elkaar: Zweeds (10 miljoen), Noors (5 miljoen), Deens (5 miljoen) en IJslands (0,3 miljoen).</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Scheikunde</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Scheikunde</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hoeveel graden Celsius is het vriespunt van water bij normale luchtdruk?</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>How many degrees Celsius is the freezing point of water at normal air pressure?</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://webbook.nist.gov/cgi/cbook.cgi?ID=C7732185</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Celsius</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>De celsiusschaal is gedefinieerd met de volgende twee ijkpunten:
+0 °C (0 graden Celsius) is de temperatuur waarbij water bevriest bij een luchtdruk van 1 atmosfeer.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>